--- a/data/sars/pacific/tables/Pacific_2015_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2015_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF20A8A-4A9A-8142-9F8F-F8984E85AE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6D277F-5FC7-E14C-B6B4-F6F77818A43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="31100" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="122">
   <si>
     <t>California sea lion (U.S.)</t>
   </si>
@@ -367,10 +367,25 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>RF=0.2 in SAR; RF=0.1 was typo in table</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.4 was typo in table</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -381,7 +396,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -398,6 +413,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -425,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -479,6 +500,9 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -784,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="23.3984375" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="56.59765625" style="2" bestFit="1" customWidth="1"/>
@@ -798,12 +822,13 @@
     <col min="9" max="9" width="14.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.796875" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="23.3984375" style="2"/>
+    <col min="14" max="14" width="12" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.59765625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="42" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="23.3984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
@@ -820,7 +845,7 @@
         <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>108</v>
@@ -844,10 +869,16 @@
         <v>114</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+        <v>119</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,8 +921,9 @@
       <c r="N2" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O2" s="9"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -934,8 +966,9 @@
       <c r="N3" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -974,8 +1007,9 @@
       <c r="N4" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O4" s="9"/>
+    </row>
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,8 +1048,9 @@
       <c r="N5" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O5" s="9"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1054,8 +1089,9 @@
       <c r="N6" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O6" s="9"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1094,8 +1130,9 @@
       <c r="N7" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1138,8 +1175,9 @@
       <c r="N8" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O8" s="9"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1178,8 +1216,9 @@
       <c r="N9" s="9">
         <v>2000</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O9" s="9"/>
+    </row>
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -1222,8 +1261,11 @@
       <c r="N10" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O10" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -1266,8 +1308,11 @@
       <c r="N11" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O11" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1310,8 +1355,9 @@
       <c r="N12" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O12" s="9"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -1354,8 +1400,9 @@
       <c r="N13" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O13" s="9"/>
+    </row>
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -1398,8 +1445,9 @@
       <c r="N14" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1442,8 +1490,9 @@
       <c r="N15" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O15" s="9"/>
+    </row>
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1486,8 +1535,9 @@
       <c r="N16" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O16" s="9"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1530,8 +1580,9 @@
       <c r="N17" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O17" s="9"/>
+    </row>
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -1574,8 +1625,9 @@
       <c r="N18" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="30" x14ac:dyDescent="0.15">
+      <c r="O18" s="9"/>
+    </row>
+    <row r="19" spans="1:15" ht="30" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -1618,8 +1670,9 @@
       <c r="N19" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O19" s="9"/>
+    </row>
+    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -1662,8 +1715,9 @@
       <c r="N20" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -1706,8 +1760,9 @@
       <c r="N21" s="9">
         <v>2008</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.15">
+      <c r="O21" s="9"/>
+    </row>
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1750,8 +1805,9 @@
       <c r="N22" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O22" s="9"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -1794,8 +1850,9 @@
       <c r="N23" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="30" x14ac:dyDescent="0.15">
+      <c r="O23" s="9"/>
+    </row>
+    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -1838,8 +1895,9 @@
       <c r="N24" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O24" s="9"/>
+    </row>
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -1882,8 +1940,9 @@
       <c r="N25" s="9">
         <v>2012</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.15">
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
@@ -1926,8 +1985,9 @@
       <c r="N26" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O26" s="9"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
@@ -1970,8 +2030,9 @@
       <c r="N27" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O27" s="9"/>
+    </row>
+    <row r="28" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>39</v>
       </c>
@@ -2014,8 +2075,11 @@
       <c r="N28" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O28" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>40</v>
       </c>
@@ -2058,8 +2122,9 @@
       <c r="N29" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O29" s="9"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>41</v>
       </c>
@@ -2102,8 +2167,9 @@
       <c r="N30" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.15">
+      <c r="O30" s="9"/>
+    </row>
+    <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
@@ -2146,8 +2212,9 @@
       <c r="N31" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O31" s="9"/>
+    </row>
+    <row r="32" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
@@ -2190,8 +2257,9 @@
       <c r="N32" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O32" s="9"/>
+    </row>
+    <row r="33" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>44</v>
       </c>
@@ -2234,8 +2302,9 @@
       <c r="N33" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>45</v>
       </c>
@@ -2278,8 +2347,9 @@
       <c r="N34" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O34" s="9"/>
+    </row>
+    <row r="35" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,8 +2392,9 @@
       <c r="N35" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O35" s="9"/>
+    </row>
+    <row r="36" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
@@ -2366,8 +2437,9 @@
       <c r="N36" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O36" s="9"/>
+    </row>
+    <row r="37" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>48</v>
       </c>
@@ -2406,8 +2478,9 @@
       <c r="N37" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O37" s="9"/>
+    </row>
+    <row r="38" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>49</v>
       </c>
@@ -2450,8 +2523,9 @@
       <c r="N38" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O38" s="9"/>
+    </row>
+    <row r="39" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
         <v>52</v>
       </c>
@@ -2494,8 +2568,11 @@
       <c r="N39" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O39" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
@@ -2538,8 +2615,9 @@
       <c r="N40" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O40" s="9"/>
+    </row>
+    <row r="41" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>54</v>
       </c>
@@ -2582,8 +2660,9 @@
       <c r="N41" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O41" s="9"/>
+    </row>
+    <row r="42" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
@@ -2626,8 +2705,9 @@
       <c r="N42" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O42" s="9"/>
+    </row>
+    <row r="43" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
         <v>56</v>
       </c>
@@ -2670,8 +2750,11 @@
       <c r="N43" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O43" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
@@ -2712,8 +2795,9 @@
       <c r="N44" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O44" s="9"/>
+    </row>
+    <row r="45" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>58</v>
       </c>
@@ -2756,8 +2840,9 @@
       <c r="N45" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>59</v>
       </c>
@@ -2798,8 +2883,9 @@
       <c r="N46" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O46" s="9"/>
+    </row>
+    <row r="47" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,8 +2926,9 @@
       <c r="N47" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O47" s="9"/>
+    </row>
+    <row r="48" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
@@ -2884,8 +2971,9 @@
       <c r="N48" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O48" s="9"/>
+    </row>
+    <row r="49" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>62</v>
       </c>
@@ -2928,8 +3016,9 @@
       <c r="N49" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O49" s="9"/>
+    </row>
+    <row r="50" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>63</v>
       </c>
@@ -2972,8 +3061,9 @@
       <c r="N50" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O50" s="9"/>
+    </row>
+    <row r="51" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>64</v>
       </c>
@@ -3016,8 +3106,9 @@
       <c r="N51" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O51" s="9"/>
+    </row>
+    <row r="52" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
@@ -3058,8 +3149,9 @@
       <c r="N52" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O52" s="9"/>
+    </row>
+    <row r="53" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
@@ -3098,8 +3190,9 @@
       <c r="N53" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O53" s="9"/>
+    </row>
+    <row r="54" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
@@ -3138,8 +3231,9 @@
       <c r="N54" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O54" s="9"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -3178,8 +3272,9 @@
       <c r="N55" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O55" s="9"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
@@ -3220,8 +3315,9 @@
       <c r="N56" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O56" s="9"/>
+    </row>
+    <row r="57" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>70</v>
       </c>
@@ -3264,8 +3360,9 @@
       <c r="N57" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O57" s="9"/>
+    </row>
+    <row r="58" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
@@ -3308,8 +3405,9 @@
       <c r="N58" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O58" s="9"/>
+    </row>
+    <row r="59" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>72</v>
       </c>
@@ -3352,8 +3450,9 @@
       <c r="N59" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O59" s="9"/>
+    </row>
+    <row r="60" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
@@ -3394,8 +3493,9 @@
       <c r="N60" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O60" s="9"/>
+    </row>
+    <row r="61" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>74</v>
       </c>
@@ -3434,8 +3534,9 @@
       <c r="N61" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O61" s="9"/>
+    </row>
+    <row r="62" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
@@ -3474,8 +3575,9 @@
       <c r="N62" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O62" s="9"/>
+    </row>
+    <row r="63" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>76</v>
       </c>
@@ -3516,8 +3618,9 @@
       <c r="N63" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O63" s="9"/>
+    </row>
+    <row r="64" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>77</v>
       </c>
@@ -3558,8 +3661,9 @@
       <c r="N64" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O64" s="9"/>
+    </row>
+    <row r="65" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
@@ -3600,8 +3704,9 @@
       <c r="N65" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O65" s="9"/>
+    </row>
+    <row r="66" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
@@ -3640,8 +3745,9 @@
       <c r="N66" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O66" s="9"/>
+    </row>
+    <row r="67" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>80</v>
       </c>
@@ -3682,8 +3788,9 @@
       <c r="N67" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O67" s="9"/>
+    </row>
+    <row r="68" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="4" t="s">
         <v>81</v>
       </c>
@@ -3722,8 +3829,11 @@
       <c r="N68" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O68" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="4" t="s">
         <v>82</v>
       </c>
@@ -3740,7 +3850,7 @@
         <v>0.04</v>
       </c>
       <c r="F69" s="14">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G69" s="14">
         <v>9.3000000000000007</v>
@@ -3764,8 +3874,14 @@
       <c r="N69" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O69" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>83</v>
       </c>
@@ -3804,8 +3920,9 @@
       <c r="N70" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O70" s="9"/>
+    </row>
+    <row r="71" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="4" t="s">
         <v>84</v>
       </c>
@@ -3848,8 +3965,11 @@
       <c r="N71" s="13">
         <v>2015</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O71" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>85</v>
       </c>
@@ -3892,8 +4012,9 @@
       <c r="N72" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O72" s="9"/>
+    </row>
+    <row r="73" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>86</v>
       </c>
@@ -3934,8 +4055,9 @@
       <c r="N73" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O73" s="9"/>
+    </row>
+    <row r="74" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>87</v>
       </c>
@@ -3976,8 +4098,9 @@
       <c r="N74" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O74" s="9"/>
+    </row>
+    <row r="75" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>88</v>
       </c>
@@ -4018,8 +4141,9 @@
       <c r="N75" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O75" s="9"/>
+    </row>
+    <row r="76" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>89</v>
       </c>
@@ -4060,8 +4184,9 @@
       <c r="N76" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O76" s="9"/>
+    </row>
+    <row r="77" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>90</v>
       </c>
@@ -4100,8 +4225,9 @@
       <c r="N77" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O77" s="9"/>
+    </row>
+    <row r="78" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>91</v>
       </c>
@@ -4142,8 +4268,9 @@
       <c r="N78" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O78" s="9"/>
+    </row>
+    <row r="79" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>92</v>
       </c>
@@ -4184,8 +4311,9 @@
       <c r="N79" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O79" s="9"/>
+    </row>
+    <row r="80" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>93</v>
       </c>
@@ -4202,7 +4330,7 @@
         <v>0.04</v>
       </c>
       <c r="F80" s="10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G80" s="10">
         <v>10.199999999999999</v>
@@ -4226,8 +4354,12 @@
       <c r="N80" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O80" s="9"/>
+      <c r="P80" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>94</v>
       </c>
@@ -4268,8 +4400,9 @@
       <c r="N81" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O81" s="9"/>
+    </row>
+    <row r="82" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>95</v>
       </c>
@@ -4310,8 +4443,9 @@
       <c r="N82" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O82" s="9"/>
+    </row>
+    <row r="83" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>96</v>
       </c>
@@ -4352,8 +4486,9 @@
       <c r="N83" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O83" s="9"/>
+    </row>
+    <row r="84" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>97</v>
       </c>
@@ -4394,8 +4529,9 @@
       <c r="N84" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O84" s="9"/>
+    </row>
+    <row r="85" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>98</v>
       </c>
@@ -4436,8 +4572,9 @@
       <c r="N85" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O85" s="9"/>
+    </row>
+    <row r="86" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>99</v>
       </c>
@@ -4480,8 +4617,9 @@
       <c r="N86" s="9">
         <v>2009</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O86" s="9"/>
+    </row>
+    <row r="87" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>100</v>
       </c>
@@ -4524,8 +4662,9 @@
       <c r="N87" s="9">
         <v>2008</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O87" s="9"/>
+    </row>
+    <row r="88" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>101</v>
       </c>
@@ -4568,6 +4707,7 @@
       <c r="N88" s="9">
         <v>2008</v>
       </c>
+      <c r="O88" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
